--- a/backend/METADATA.xlsx
+++ b/backend/METADATA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PB396RE\Downloads\fuzzy-deduplication - Copy (2)\backend\static_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PB396RE\Downloads\fuzzy-deduplication - Copy (2)\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84CD260D-C2D8-4C9D-87B4-78C19993BB2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D11CD111-34E7-4BA4-BF95-AD97B15A30E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F3E505C7-3873-40FC-89BC-F2226FA70B96}"/>
   </bookViews>
@@ -72,13 +72,27 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -89,7 +103,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -97,12 +111,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -437,7 +470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4114689-C68C-4E82-8A54-DFD351E4A2AB}">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="17.26953125" customWidth="1"/>
@@ -446,37 +479,42 @@
     <col min="5" max="5" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
